--- a/5. SMS Reports/.Reports/12. Dec/12.2025 SMS - CLK Distribution recommendation.xlsx
+++ b/5. SMS Reports/.Reports/12. Dec/12.2025 SMS - CLK Distribution recommendation.xlsx
@@ -492,7 +492,7 @@
     <row r="6" ht="6.75" customHeight="1"/>
     <row r="7">
       <c r="A7" s="3">
-        <f>138955.95-27213.04</f>
+        <f>12339.14-2062.33</f>
         <v/>
       </c>
       <c r="B7" s="2">
